--- a/tests/fixtures/penafiel/solicitud_servicios.xlsx
+++ b/tests/fixtures/penafiel/solicitud_servicios.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MODELO-P200</t>
+          <t>AVANT40</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MODELO-P200</t>
+          <t>AT 200</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
